--- a/data/trans_dic/P15B_3_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15B_3_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año (tasa de respuesta: 89,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,77; 66,41</t>
+          <t>22,95; 68,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,91; 37,71</t>
+          <t>15,61; 37,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 24,76</t>
+          <t>4,95; 26,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,19; 50,22</t>
+          <t>18,16; 51,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,15</t>
+          <t>0,0; 17,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 15,86</t>
+          <t>1,75; 16,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 12,69</t>
+          <t>2,35; 13,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,45; 42,43</t>
+          <t>14,32; 43,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,71; 24,02</t>
+          <t>10,16; 23,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 15,74</t>
+          <t>4,16; 16,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,26; 30,89</t>
+          <t>11,36; 30,53</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,47; 51,9</t>
+          <t>21,64; 52,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,75; 30,76</t>
+          <t>12,44; 30,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,07; 30,67</t>
+          <t>10,92; 32,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,58; 34,46</t>
+          <t>13,13; 36,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,09</t>
+          <t>0,0; 25,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,94</t>
+          <t>1,3; 11,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 19,45</t>
+          <t>2,38; 19,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,25; 36,15</t>
+          <t>14,1; 35,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 18,58</t>
+          <t>8,22; 18,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 18,05</t>
+          <t>5,55; 18,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 23,98</t>
+          <t>9,38; 23,84</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,61; 66,45</t>
+          <t>25,85; 68,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,03; 35,98</t>
+          <t>14,74; 36,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 34,54</t>
+          <t>5,86; 34,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,94; 44,5</t>
+          <t>10,32; 43,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,95; 46,49</t>
+          <t>8,38; 45,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 22,63</t>
+          <t>2,29; 22,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 33,41</t>
+          <t>6,02; 33,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,79</t>
+          <t>1,07; 9,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,47; 51,58</t>
+          <t>23,7; 51,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 24,77</t>
+          <t>10,77; 24,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,56; 27,36</t>
+          <t>8,4; 27,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 21,01</t>
+          <t>5,66; 20,95</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 23,05</t>
+          <t>2,67; 23,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 26,98</t>
+          <t>10,81; 27,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 21,65</t>
+          <t>4,81; 21,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,59; 31,65</t>
+          <t>9,26; 29,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,49</t>
+          <t>0,0; 18,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,75</t>
+          <t>0,0; 11,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 20,08</t>
+          <t>3,56; 19,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,58; 19,55</t>
+          <t>5,19; 19,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 16,69</t>
+          <t>3,11; 16,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 18,33</t>
+          <t>7,47; 18,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 16,9</t>
+          <t>5,76; 16,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 21,13</t>
+          <t>8,35; 20,45</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,11; 41,52</t>
+          <t>24,54; 40,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,25; 27,12</t>
+          <t>16,98; 26,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 20,48</t>
+          <t>10,34; 20,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,87; 30,55</t>
+          <t>17,21; 30,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 18,96</t>
+          <t>5,01; 18,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,26</t>
+          <t>2,57; 9,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,25; 11,95</t>
+          <t>4,14; 11,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 11,74</t>
+          <t>4,69; 11,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,09; 29,47</t>
+          <t>16,95; 28,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,11; 17,44</t>
+          <t>10,96; 17,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 14,55</t>
+          <t>8,14; 14,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,08; 19,7</t>
+          <t>11,54; 19,11</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año (tasa de respuesta: 89,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5187; 15129</t>
+          <t>5229; 15492</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8802; 22257</t>
+          <t>9214; 21888</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1925; 9842</t>
+          <t>1969; 10668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8164; 22541</t>
+          <t>8151; 23077</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1768</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 8477</t>
+          <t>0; 9420</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>841; 7721</t>
+          <t>854; 8219</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>960; 5486</t>
+          <t>1017; 5682</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5198; 16400</t>
+          <t>5536; 16835</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10826; 26779</t>
+          <t>11327; 26460</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2999; 13921</t>
+          <t>3678; 14448</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9925; 27220</t>
+          <t>10014; 26902</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9184; 22201</t>
+          <t>9259; 22402</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10366; 25005</t>
+          <t>10111; 24430</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6091; 18547</t>
+          <t>6602; 19785</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7655; 22787</t>
+          <t>8685; 23881</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6658</t>
+          <t>0; 7672</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>958; 8912</t>
+          <t>967; 8584</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2064</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1323; 11134</t>
+          <t>1360; 11138</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10388; 26356</t>
+          <t>10282; 25615</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12111; 28976</t>
+          <t>12809; 29525</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6081; 19691</t>
+          <t>6053; 19969</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11744; 29586</t>
+          <t>11576; 29415</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5859; 15818</t>
+          <t>6154; 16203</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8780; 21017</t>
+          <t>8608; 21535</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2160; 12665</t>
+          <t>2147; 12645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2907; 13010</t>
+          <t>3018; 12760</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2882; 11210</t>
+          <t>2022; 10995</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1956; 12909</t>
+          <t>1306; 12879</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1955; 10543</t>
+          <t>1901; 10420</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>465; 4317</t>
+          <t>470; 4250</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11248; 24719</t>
+          <t>11359; 24461</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12688; 28600</t>
+          <t>12434; 28686</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5842; 18668</t>
+          <t>5731; 18720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4002; 15407</t>
+          <t>4152; 15366</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>898; 7769</t>
+          <t>899; 7974</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10200; 23810</t>
+          <t>9536; 24380</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2993; 13184</t>
+          <t>2928; 12914</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5056; 18639</t>
+          <t>5452; 17077</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4380</t>
+          <t>0; 4354</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6949</t>
+          <t>0; 7982</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2946; 12571</t>
+          <t>2229; 12047</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3852; 13493</t>
+          <t>3583; 13166</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1740; 9579</t>
+          <t>1784; 9580</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11303; 29245</t>
+          <t>11916; 29583</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7768; 20878</t>
+          <t>7118; 20733</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10972; 27032</t>
+          <t>10685; 26159</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29670; 51103</t>
+          <t>30208; 50354</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>49496; 77841</t>
+          <t>48742; 76648</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20213; 40504</t>
+          <t>20451; 40329</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33598; 60830</t>
+          <t>34267; 61139</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4963; 17783</t>
+          <t>4703; 17075</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6941; 23649</t>
+          <t>6561; 23133</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8146; 22882</t>
+          <t>7920; 21957</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10073; 25071</t>
+          <t>10027; 24561</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37066; 63918</t>
+          <t>36767; 62093</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60244; 94567</t>
+          <t>59450; 94118</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31716; 56626</t>
+          <t>31690; 57225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>49842; 81321</t>
+          <t>47614; 78884</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15B_3_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15B_3_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,95; 68,0</t>
+          <t>25,72; 68,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,61; 37,08</t>
+          <t>16,24; 38,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 26,84</t>
+          <t>4,92; 25,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,16; 51,42</t>
+          <t>16,26; 51,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,95</t>
+          <t>0,0; 16,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 16,89</t>
+          <t>1,67; 15,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 13,14</t>
+          <t>2,17; 12,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,32; 43,56</t>
+          <t>13,18; 42,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,16; 23,73</t>
+          <t>9,82; 23,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 16,34</t>
+          <t>4,32; 16,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,36; 30,53</t>
+          <t>10,99; 31,36</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,64; 52,36</t>
+          <t>20,15; 50,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,44; 30,05</t>
+          <t>12,25; 30,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,92; 32,72</t>
+          <t>10,57; 30,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,13; 36,11</t>
+          <t>13,08; 36,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,46</t>
+          <t>0,0; 24,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 11,5</t>
+          <t>1,29; 11,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 19,46</t>
+          <t>2,07; 19,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,1; 35,13</t>
+          <t>13,71; 34,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,22; 18,94</t>
+          <t>8,26; 18,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 18,31</t>
+          <t>5,56; 17,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 23,84</t>
+          <t>9,74; 23,79</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,85; 68,06</t>
+          <t>25,97; 65,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,74; 36,87</t>
+          <t>14,59; 36,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 34,49</t>
+          <t>5,56; 33,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,32; 43,65</t>
+          <t>8,22; 39,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,38; 45,6</t>
+          <t>11,75; 49,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 22,58</t>
+          <t>3,02; 22,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 33,01</t>
+          <t>6,14; 33,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,64</t>
+          <t>0,91; 9,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,7; 51,05</t>
+          <t>23,32; 51,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,77; 24,85</t>
+          <t>10,2; 24,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,4; 27,44</t>
+          <t>8,61; 28,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 20,95</t>
+          <t>4,52; 18,85</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 23,65</t>
+          <t>2,64; 24,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,81; 27,63</t>
+          <t>11,63; 28,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 21,21</t>
+          <t>4,82; 21,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,26; 29,0</t>
+          <t>8,51; 29,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,38</t>
+          <t>0,0; 22,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,2</t>
+          <t>0,0; 10,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 19,24</t>
+          <t>3,29; 20,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 19,08</t>
+          <t>5,48; 18,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 16,69</t>
+          <t>2,95; 16,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 18,55</t>
+          <t>7,2; 17,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,76; 16,79</t>
+          <t>5,64; 17,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,35; 20,45</t>
+          <t>8,49; 19,67</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,54; 40,91</t>
+          <t>24,28; 42,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,98; 26,71</t>
+          <t>17,04; 26,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 20,39</t>
+          <t>10,14; 20,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,21; 30,7</t>
+          <t>16,94; 30,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 18,2</t>
+          <t>4,76; 18,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,06</t>
+          <t>2,74; 9,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 11,47</t>
+          <t>4,23; 11,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 11,5</t>
+          <t>4,59; 11,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,95; 28,63</t>
+          <t>17,34; 28,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,96; 17,35</t>
+          <t>11,15; 17,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,14; 14,7</t>
+          <t>8,42; 15,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,54; 19,11</t>
+          <t>11,51; 18,72</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14270</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16831</t>
+          <t>17781</t>
         </is>
       </c>
     </row>
@@ -1645,22 +1645,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5229; 15492</t>
+          <t>5860; 15577</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9214; 21888</t>
+          <t>9583; 22774</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1969; 10668</t>
+          <t>1957; 10062</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8151; 23077</t>
+          <t>8079; 25555</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,37 +1670,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 9420</t>
+          <t>0; 8486</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>854; 8219</t>
+          <t>813; 7726</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1017; 5682</t>
+          <t>1020; 5982</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5536; 16835</t>
+          <t>5096; 16539</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11327; 26460</t>
+          <t>10947; 26509</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3678; 14448</t>
+          <t>3822; 14566</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10014; 26902</t>
+          <t>10622; 30300</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>21469</t>
         </is>
       </c>
     </row>
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9259; 22402</t>
+          <t>8619; 21734</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10111; 24430</t>
+          <t>9957; 24990</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6602; 19785</t>
+          <t>6394; 18625</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8685; 23881</t>
+          <t>9638; 27155</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7672</t>
+          <t>0; 7529</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>967; 8584</t>
+          <t>963; 8692</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1888,27 +1888,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1360; 11138</t>
+          <t>1299; 12103</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10282; 25615</t>
+          <t>9994; 25286</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12809; 29525</t>
+          <t>12880; 29174</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6053; 19969</t>
+          <t>6060; 19190</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11576; 29415</t>
+          <t>13295; 32471</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8677</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6154; 16203</t>
+          <t>6183; 15697</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8608; 21535</t>
+          <t>8524; 21234</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2147; 12645</t>
+          <t>2039; 12134</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3018; 12760</t>
+          <t>2711; 13161</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2022; 10995</t>
+          <t>2832; 11843</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1306; 12879</t>
+          <t>1722; 12844</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1901; 10420</t>
+          <t>1938; 10541</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>470; 4250</t>
+          <t>449; 4463</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11359; 24461</t>
+          <t>11174; 24495</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12434; 28686</t>
+          <t>11779; 28624</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5731; 18720</t>
+          <t>5874; 19748</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4152; 15366</t>
+          <t>3724; 15544</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10540</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>18149</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>899; 7974</t>
+          <t>890; 8186</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9536; 24380</t>
+          <t>10265; 24805</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2928; 12914</t>
+          <t>2937; 13330</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5452; 17077</t>
+          <t>5409; 18620</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4354</t>
+          <t>0; 5418</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 7982</t>
+          <t>0; 7294</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2229; 12047</t>
+          <t>2061; 12604</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3583; 13166</t>
+          <t>4001; 13812</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1784; 9580</t>
+          <t>1693; 9437</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11916; 29583</t>
+          <t>11485; 28689</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7118; 20733</t>
+          <t>6963; 21423</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10685; 26159</t>
+          <t>11589; 26853</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46487</t>
+          <t>49506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62259</t>
+          <t>66076</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30208; 50354</t>
+          <t>29880; 51811</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48742; 76648</t>
+          <t>48908; 76630</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20451; 40329</t>
+          <t>20044; 40235</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34267; 61139</t>
+          <t>37246; 66343</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4703; 17075</t>
+          <t>4464; 16998</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6561; 23133</t>
+          <t>7005; 23025</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7920; 21957</t>
+          <t>8102; 22800</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10027; 24561</t>
+          <t>10660; 26274</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36767; 62093</t>
+          <t>37616; 62717</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>59450; 94118</t>
+          <t>60449; 92848</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31690; 57225</t>
+          <t>32791; 58691</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>47614; 78884</t>
+          <t>52043; 84630</t>
         </is>
       </c>
     </row>
